--- a/InputData/bldgs/RPbBCT/Rebate Perc by Building Component Type.xlsx
+++ b/InputData/bldgs/RPbBCT/Rebate Perc by Building Component Type.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="22827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeff-nonadmin\CodeRepositories\eps-us\InputData\bldgs\RPbBCT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RobbieOrvis\Models\EPS Structure Research\eps-us-dc-replay\InputData\bldgs\RPbBCT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5188199D-076B-459F-9A6C-A672B4FCF82B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15C89B63-9B77-46B1-8260-C82043620C3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1335" yWindow="945" windowWidth="24765" windowHeight="16080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="23520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -25,6 +25,9 @@
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -32,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="53">
   <si>
     <t>Sources:</t>
   </si>
@@ -182,6 +185,15 @@
   </si>
   <si>
     <t>less generous.</t>
+  </si>
+  <si>
+    <t>data centers</t>
+  </si>
+  <si>
+    <t>Data centers</t>
+  </si>
+  <si>
+    <t>Data centers are a separate building type. The data-centers column copies commercial so the value is defined, but the building component rebate policy is not applied to data centers.</t>
   </si>
 </sst>
 </file>
@@ -192,7 +204,7 @@
     <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
     <numFmt numFmtId="164" formatCode="0.0000"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
-    <numFmt numFmtId="173" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
@@ -335,7 +347,7 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
@@ -354,16 +366,16 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="9"/>
     <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="10">
     <cellStyle name="Body: normal cell" xfId="5" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -391,9 +403,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -431,9 +443,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -466,26 +478,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -518,26 +513,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -711,7 +689,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="58.42578125" customWidth="1"/>
@@ -746,7 +724,7 @@
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="11" t="s">
         <v>15</v>
       </c>
     </row>
@@ -776,7 +754,7 @@
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="11" t="s">
         <v>19</v>
       </c>
     </row>
@@ -831,11 +809,19 @@
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="16">
+      <c r="A28" s="14">
         <v>1.2477934782608695</v>
       </c>
       <c r="B28" t="s">
         <v>40</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="60" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B30" s="15" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -876,13 +862,13 @@
       <c r="A3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="D3" s="13" t="s">
         <v>29</v>
       </c>
     </row>
@@ -890,10 +876,10 @@
       <c r="A4" t="s">
         <v>25</v>
       </c>
-      <c r="B4" s="14">
+      <c r="B4" s="12">
         <v>121</v>
       </c>
-      <c r="C4" s="14">
+      <c r="C4" s="12">
         <v>876</v>
       </c>
       <c r="D4" s="2">
@@ -905,10 +891,10 @@
       <c r="A5" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="14">
+      <c r="B5" s="12">
         <v>360</v>
       </c>
-      <c r="C5" s="14">
+      <c r="C5" s="12">
         <v>5137</v>
       </c>
       <c r="D5" s="2">
@@ -920,10 +906,10 @@
       <c r="A6" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="14">
+      <c r="B6" s="12">
         <v>191</v>
       </c>
-      <c r="C6" s="14">
+      <c r="C6" s="12">
         <v>1106</v>
       </c>
       <c r="D6" s="2">
@@ -953,48 +939,48 @@
       <c r="A15" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="B15" s="15" t="s">
+      <c r="B15" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="15" t="s">
+      <c r="C15" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D15" s="15"/>
+      <c r="D15" s="13"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>31</v>
       </c>
-      <c r="B16" s="14">
+      <c r="B16" s="12">
         <v>69.698999999999998</v>
       </c>
-      <c r="C16" s="14">
+      <c r="C16" s="12">
         <f>B16*About!$A$28</f>
         <v>86.969957641304347</v>
       </c>
-      <c r="D16" s="14"/>
+      <c r="D16" s="12"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="14">
+      <c r="B17" s="12">
         <v>34.746000000000002</v>
       </c>
-      <c r="C17" s="14">
+      <c r="C17" s="12">
         <f>B17*About!$A$28</f>
         <v>43.355832195652177</v>
       </c>
-      <c r="D17" s="14"/>
+      <c r="D17" s="12"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>33</v>
       </c>
-      <c r="B18" s="14">
+      <c r="B18" s="12">
         <v>50.64</v>
       </c>
-      <c r="C18" s="14">
+      <c r="C18" s="12">
         <f>B18*About!$A$28</f>
         <v>63.188261739130432</v>
       </c>
@@ -1014,7 +1000,7 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -1023,7 +1009,7 @@
     <col min="4" max="4" width="14.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
         <v>12</v>
       </c>
@@ -1036,109 +1022,134 @@
       <c r="D1" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="17">
+      <c r="B2" s="14">
         <f>Data!$D$5</f>
         <v>7.0079813120498352E-2</v>
       </c>
-      <c r="C2" s="17">
+      <c r="C2" s="14">
         <f>$B2</f>
         <v>7.0079813120498352E-2</v>
       </c>
-      <c r="D2" s="17">
+      <c r="D2" s="14">
         <f>$B2</f>
         <v>7.0079813120498352E-2</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E2" s="14">
+        <f>$D2</f>
+        <v>7.0079813120498352E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="17">
+      <c r="B3" s="14">
         <f>Data!$D$5</f>
         <v>7.0079813120498352E-2</v>
       </c>
-      <c r="C3" s="17">
+      <c r="C3" s="14">
         <f t="shared" ref="C3:D7" si="0">$B3</f>
         <v>7.0079813120498352E-2</v>
       </c>
-      <c r="D3" s="17">
+      <c r="D3" s="14">
         <f t="shared" si="0"/>
         <v>7.0079813120498352E-2</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E3" s="14">
+        <f>$D3</f>
+        <v>7.0079813120498352E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="11">
-        <v>0</v>
-      </c>
-      <c r="C4" s="11">
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D4" s="11">
+      <c r="D4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E4">
+        <f>$D4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="11">
-        <v>0</v>
-      </c>
-      <c r="C5" s="11">
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D5" s="11">
+      <c r="D5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E5">
+        <f>$D5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="17">
+      <c r="B6" s="14">
         <f>Data!D4</f>
         <v>0.13812785388127855</v>
       </c>
-      <c r="C6" s="17">
+      <c r="C6" s="14">
         <f t="shared" si="0"/>
         <v>0.13812785388127855</v>
       </c>
-      <c r="D6" s="17">
+      <c r="D6" s="14">
         <f t="shared" si="0"/>
         <v>0.13812785388127855</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E6" s="14">
+        <f>$D6</f>
+        <v>0.13812785388127855</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="11">
-        <v>0</v>
-      </c>
-      <c r="C7" s="11">
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D7" s="11">
+      <c r="D7">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B8" s="12"/>
-      <c r="C8" s="12"/>
+      <c r="E7">
+        <f>$D7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D8" s="10"/>
     </row>
   </sheetData>
